--- a/IPC.xlsx
+++ b/IPC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmacity.sharepoint.com/sites/PerformanceEficiencia/Shared Documents/2025/Automatización/Tablero CAPEX/app ajuste roi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D0E3F6F-84E3-40A6-AB72-BA6859007450}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95EA5BE7-EA0F-4DC3-8273-2D144AC6C6E8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B117CEED-1A99-47C6-982B-3272E3DCE7F9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{B117CEED-1A99-47C6-982B-3272E3DCE7F9}"/>
   </bookViews>
   <sheets>
     <sheet name="IPC" sheetId="1" r:id="rId1"/>
@@ -84,12 +84,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,8 +159,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,6 +222,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -235,7 +270,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -273,6 +308,10 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -351,33 +390,6 @@
           <cell r="M2">
             <v>2.3E-2</v>
           </cell>
-          <cell r="S2">
-            <v>1.8508353880333336E-2</v>
-          </cell>
-          <cell r="T2">
-            <v>1.7400357333333335E-2</v>
-          </cell>
-          <cell r="U2">
-            <v>1.6734340126266668E-2</v>
-          </cell>
-          <cell r="V2">
-            <v>1.6459823760600002E-2</v>
-          </cell>
-          <cell r="W2">
-            <v>1.6570618273733333E-2</v>
-          </cell>
-          <cell r="X2">
-            <v>1.6099733867993835E-2</v>
-          </cell>
-          <cell r="Y2">
-            <v>1.5785369711999998E-2</v>
-          </cell>
-          <cell r="Z2">
-            <v>1.4813698632497133E-2</v>
-          </cell>
-          <cell r="AA2">
-            <v>1.5666789785585333E-2</v>
-          </cell>
         </row>
         <row r="7">
           <cell r="B7">
@@ -415,33 +427,6 @@
           </cell>
           <cell r="M7">
             <v>1480</v>
-          </cell>
-          <cell r="S7">
-            <v>1582</v>
-          </cell>
-          <cell r="T7">
-            <v>1612</v>
-          </cell>
-          <cell r="U7">
-            <v>1642</v>
-          </cell>
-          <cell r="V7">
-            <v>1673</v>
-          </cell>
-          <cell r="W7">
-            <v>1704</v>
-          </cell>
-          <cell r="X7">
-            <v>1731</v>
-          </cell>
-          <cell r="Y7">
-            <v>1759</v>
-          </cell>
-          <cell r="Z7">
-            <v>1795</v>
-          </cell>
-          <cell r="AA7">
-            <v>1827</v>
           </cell>
         </row>
       </sheetData>
@@ -2873,10 +2858,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B618453-A551-4EAE-981C-0CD6ACA85DD7}">
-  <dimension ref="A1:BU3"/>
+  <dimension ref="A1:CG3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B1" s="19">
         <v>44197</v>
       </c>
@@ -3093,8 +3078,44 @@
       <c r="BU1" s="20">
         <v>46357</v>
       </c>
+      <c r="BV1" s="19">
+        <v>46388</v>
+      </c>
+      <c r="BW1" s="20">
+        <v>46419</v>
+      </c>
+      <c r="BX1" s="20">
+        <v>46447</v>
+      </c>
+      <c r="BY1" s="20">
+        <v>46478</v>
+      </c>
+      <c r="BZ1" s="20">
+        <v>46508</v>
+      </c>
+      <c r="CA1" s="20">
+        <v>46539</v>
+      </c>
+      <c r="CB1" s="20">
+        <v>46569</v>
+      </c>
+      <c r="CC1" s="20">
+        <v>46600</v>
+      </c>
+      <c r="CD1" s="20">
+        <v>46631</v>
+      </c>
+      <c r="CE1" s="20">
+        <v>46661</v>
+      </c>
+      <c r="CF1" s="19">
+        <v>46692</v>
+      </c>
+      <c r="CG1" s="20">
+        <v>46722</v>
+      </c>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3296,47 +3317,74 @@
       <c r="BK2" s="18">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="BL2" s="18">
-        <v>3.3799999999999997E-2</v>
-      </c>
-      <c r="BM2" s="18">
-        <f>'[1]Resumen Pautas'!S2</f>
-        <v>1.8508353880333336E-2</v>
-      </c>
-      <c r="BN2" s="18">
-        <f>'[1]Resumen Pautas'!T2</f>
-        <v>1.7400357333333335E-2</v>
-      </c>
-      <c r="BO2" s="18">
-        <f>'[1]Resumen Pautas'!U2</f>
-        <v>1.6734340126266668E-2</v>
-      </c>
-      <c r="BP2" s="18">
-        <f>'[1]Resumen Pautas'!V2</f>
-        <v>1.6459823760600002E-2</v>
-      </c>
-      <c r="BQ2" s="18">
-        <f>'[1]Resumen Pautas'!W2</f>
-        <v>1.6570618273733333E-2</v>
-      </c>
-      <c r="BR2" s="18">
-        <f>'[1]Resumen Pautas'!X2</f>
-        <v>1.6099733867993835E-2</v>
-      </c>
-      <c r="BS2" s="18">
-        <f>'[1]Resumen Pautas'!Y2</f>
-        <v>1.5785369711999998E-2</v>
-      </c>
-      <c r="BT2" s="18">
-        <f>'[1]Resumen Pautas'!Z2</f>
-        <v>1.4813698632497133E-2</v>
-      </c>
-      <c r="BU2" s="18">
-        <f>'[1]Resumen Pautas'!AA2</f>
-        <v>1.5666789785585333E-2</v>
+      <c r="BL2" s="23">
+        <v>3.4</v>
+      </c>
+      <c r="BM2" s="24">
+        <v>2.58</v>
+      </c>
+      <c r="BN2" s="24">
+        <v>2.15</v>
+      </c>
+      <c r="BO2" s="24">
+        <v>1.89</v>
+      </c>
+      <c r="BP2" s="24">
+        <v>2.1</v>
+      </c>
+      <c r="BQ2" s="24">
+        <v>1.66</v>
+      </c>
+      <c r="BR2" s="25">
+        <v>1.7941135008685331E-2</v>
+      </c>
+      <c r="BS2" s="25">
+        <v>1.7741632872337668E-2</v>
+      </c>
+      <c r="BT2" s="25">
+        <v>1.6766766533333335E-2</v>
+      </c>
+      <c r="BU2" s="26">
+        <v>1.8646606675666668E-2</v>
+      </c>
+      <c r="BV2" s="25">
+        <v>1.6978522750999998E-2</v>
+      </c>
+      <c r="BW2" s="25">
+        <v>1.6166797882333332E-2</v>
+      </c>
+      <c r="BX2" s="25">
+        <v>1.8417340000000001E-2</v>
+      </c>
+      <c r="BY2" s="25">
+        <v>1.6978667925E-2</v>
+      </c>
+      <c r="BZ2" s="25">
+        <v>1.5122849043291664E-2</v>
+      </c>
+      <c r="CA2" s="25">
+        <v>1.6477400975000001E-2</v>
+      </c>
+      <c r="CB2" s="25">
+        <v>1.7777374319673998E-2</v>
+      </c>
+      <c r="CC2" s="25">
+        <v>1.8766162070633332E-2</v>
+      </c>
+      <c r="CD2" s="25">
+        <v>1.8151390219999997E-2</v>
+      </c>
+      <c r="CE2" s="25">
+        <v>1.7650344553000002E-2</v>
+      </c>
+      <c r="CF2" s="25">
+        <v>1.7831109519666669E-2</v>
+      </c>
+      <c r="CG2" s="26">
+        <v>1.9100131187000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3470,40 +3518,67 @@
         <v>1400</v>
       </c>
       <c r="BM3" s="21">
-        <f>'[1]Resumen Pautas'!S7</f>
-        <v>1582</v>
+        <v>1430</v>
       </c>
       <c r="BN3" s="21">
-        <f>'[1]Resumen Pautas'!T7</f>
-        <v>1612</v>
+        <v>1450</v>
       </c>
       <c r="BO3" s="21">
-        <f>'[1]Resumen Pautas'!U7</f>
-        <v>1642</v>
+        <v>1470</v>
       </c>
       <c r="BP3" s="21">
-        <f>'[1]Resumen Pautas'!V7</f>
-        <v>1673</v>
+        <v>1490</v>
       </c>
       <c r="BQ3" s="21">
-        <f>'[1]Resumen Pautas'!W7</f>
-        <v>1704</v>
+        <v>1510</v>
       </c>
       <c r="BR3" s="21">
-        <f>'[1]Resumen Pautas'!X7</f>
-        <v>1731</v>
+        <v>1530</v>
       </c>
       <c r="BS3" s="21">
-        <f>'[1]Resumen Pautas'!Y7</f>
-        <v>1759</v>
+        <v>1550</v>
       </c>
       <c r="BT3" s="21">
-        <f>'[1]Resumen Pautas'!Z7</f>
-        <v>1795</v>
+        <v>1570</v>
       </c>
       <c r="BU3" s="21">
-        <f>'[1]Resumen Pautas'!AA7</f>
-        <v>1827</v>
+        <v>1600</v>
+      </c>
+      <c r="BV3" s="21">
+        <v>1614.44444444444</v>
+      </c>
+      <c r="BW3" s="21">
+        <v>1635.1111111111099</v>
+      </c>
+      <c r="BX3" s="21">
+        <v>1655.7777777777801</v>
+      </c>
+      <c r="BY3" s="21">
+        <v>1676.44444444444</v>
+      </c>
+      <c r="BZ3" s="21">
+        <v>1697.1111111111099</v>
+      </c>
+      <c r="CA3" s="21">
+        <v>1717.7777777777801</v>
+      </c>
+      <c r="CB3" s="21">
+        <v>1738.44444444444</v>
+      </c>
+      <c r="CC3" s="21">
+        <v>1759.1111111111099</v>
+      </c>
+      <c r="CD3" s="21">
+        <v>1779.7777777777801</v>
+      </c>
+      <c r="CE3" s="21">
+        <v>1800.44444444444</v>
+      </c>
+      <c r="CF3" s="21">
+        <v>1821.1111111111099</v>
+      </c>
+      <c r="CG3" s="21">
+        <v>1841.7777777777801</v>
       </c>
     </row>
   </sheetData>
@@ -3532,17 +3607,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dd3ed0ad-465b-4b94-9e03-9fde07fe233a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="12e925e7-9bc7-4479-8e5e-5ed9012e158e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D20E8A0A3F7A044EAC1D8300FB25DCEE" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73702fa23d3410e8aedc2854b133fdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dd3ed0ad-465b-4b94-9e03-9fde07fe233a" xmlns:ns3="12e925e7-9bc7-4479-8e5e-5ed9012e158e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29d7ad22752d16cb4316e7690fb516c1" ns2:_="" ns3:_="">
     <xsd:import namespace="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
@@ -3771,6 +3835,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dd3ed0ad-465b-4b94-9e03-9fde07fe233a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="12e925e7-9bc7-4479-8e5e-5ed9012e158e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3781,17 +3856,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6571B10-6268-4B6F-AD0A-74EA79A3E4A5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
-    <ds:schemaRef ds:uri="12e925e7-9bc7-4479-8e5e-5ed9012e158e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B3155F2-060D-48C0-AE23-D24D9B3AA2C6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3810,6 +3874,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6571B10-6268-4B6F-AD0A-74EA79A3E4A5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
+    <ds:schemaRef ds:uri="12e925e7-9bc7-4479-8e5e-5ed9012e158e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8891529D-FF05-405E-9396-D68A841F8ED5}">
   <ds:schemaRefs>

--- a/IPC.xlsx
+++ b/IPC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmacity.sharepoint.com/sites/PerformanceEficiencia/Shared Documents/2025/Automatización/Tablero CAPEX/app ajuste roi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95EA5BE7-EA0F-4DC3-8273-2D144AC6C6E8}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="13_ncr:1_{58C70089-FDDF-4DDD-8F55-2AFFFFA42B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39014294-4200-4A9C-8865-113FEE5BCE29}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{B117CEED-1A99-47C6-982B-3272E3DCE7F9}"/>
   </bookViews>
@@ -437,6 +437,10 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -3530,55 +3534,55 @@
         <v>1490</v>
       </c>
       <c r="BQ3" s="21">
-        <v>1510</v>
+        <v>1510.1562000000001</v>
       </c>
       <c r="BR3" s="21">
-        <v>1530</v>
+        <v>1540.7342880371009</v>
       </c>
       <c r="BS3" s="21">
-        <v>1550</v>
+        <v>1581.9645197555844</v>
       </c>
       <c r="BT3" s="21">
-        <v>1570</v>
+        <v>1629.6440772707538</v>
       </c>
       <c r="BU3" s="21">
-        <v>1600</v>
+        <v>1674.3315192637649</v>
       </c>
       <c r="BV3" s="21">
-        <v>1614.44444444444</v>
+        <v>1698.065306014875</v>
       </c>
       <c r="BW3" s="21">
-        <v>1635.1111111111099</v>
+        <v>1724.8714289758491</v>
       </c>
       <c r="BX3" s="21">
-        <v>1655.7777777777801</v>
+        <v>1750.869483539135</v>
       </c>
       <c r="BY3" s="21">
-        <v>1676.44444444444</v>
+        <v>1776.4807657368685</v>
       </c>
       <c r="BZ3" s="21">
-        <v>1697.1111111111099</v>
+        <v>1820.8730329908315</v>
       </c>
       <c r="CA3" s="21">
-        <v>1717.7777777777801</v>
+        <v>1875.8886716883728</v>
       </c>
       <c r="CB3" s="21">
-        <v>1738.44444444444</v>
+        <v>1945.9965580682967</v>
       </c>
       <c r="CC3" s="21">
-        <v>1759.1111111111099</v>
+        <v>2011.1019529235512</v>
       </c>
       <c r="CD3" s="21">
-        <v>1779.7777777777801</v>
+        <v>2076.2781998461815</v>
       </c>
       <c r="CE3" s="21">
-        <v>1800.44444444444</v>
+        <v>2110.6769877035927</v>
       </c>
       <c r="CF3" s="21">
-        <v>1821.1111111111099</v>
+        <v>2120.6334461887559</v>
       </c>
       <c r="CG3" s="21">
-        <v>1841.7777777777801</v>
+        <v>2130.1032880512425</v>
       </c>
     </row>
   </sheetData>
@@ -3607,6 +3611,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dd3ed0ad-465b-4b94-9e03-9fde07fe233a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="12e925e7-9bc7-4479-8e5e-5ed9012e158e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D20E8A0A3F7A044EAC1D8300FB25DCEE" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73702fa23d3410e8aedc2854b133fdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dd3ed0ad-465b-4b94-9e03-9fde07fe233a" xmlns:ns3="12e925e7-9bc7-4479-8e5e-5ed9012e158e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29d7ad22752d16cb4316e7690fb516c1" ns2:_="" ns3:_="">
     <xsd:import namespace="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
@@ -3835,27 +3859,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dd3ed0ad-465b-4b94-9e03-9fde07fe233a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="12e925e7-9bc7-4479-8e5e-5ed9012e158e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8891529D-FF05-405E-9396-D68A841F8ED5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6571B10-6268-4B6F-AD0A-74EA79A3E4A5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
+    <ds:schemaRef ds:uri="12e925e7-9bc7-4479-8e5e-5ed9012e158e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B3155F2-060D-48C0-AE23-D24D9B3AA2C6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3872,23 +3895,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6571B10-6268-4B6F-AD0A-74EA79A3E4A5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dd3ed0ad-465b-4b94-9e03-9fde07fe233a"/>
-    <ds:schemaRef ds:uri="12e925e7-9bc7-4479-8e5e-5ed9012e158e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8891529D-FF05-405E-9396-D68A841F8ED5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>